--- a/cypress/fixtures/ReferenciasPN.xlsx
+++ b/cypress/fixtures/ReferenciasPN.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="73">
   <si>
     <t>tieneReferenciasBancarias</t>
   </si>
@@ -67,7 +67,7 @@
     <t>institucionPrestamoReferenciaLaboralCliente</t>
   </si>
   <si>
-    <t>No</t>
+    <t>Si</t>
   </si>
   <si>
     <t>Cuentas</t>
@@ -76,7 +76,7 @@
     <t>Local</t>
   </si>
   <si>
-    <t>25145010000017</t>
+    <t>25145010000021</t>
   </si>
   <si>
     <t>Monetarios</t>
@@ -91,7 +91,7 @@
     <t>Tarjetas</t>
   </si>
   <si>
-    <t>2787960000000004</t>
+    <t>2787960000000005</t>
   </si>
   <si>
     <t>Visa Oro</t>
@@ -104,6 +104,9 @@
   </si>
   <si>
     <t>Banco atlantida, s.a.</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
   <si>
     <t>tieneReferenciasComerciales</t>
@@ -136,13 +139,13 @@
     <t>Correo Personal</t>
   </si>
   <si>
-    <t>alberto690@gmail.com</t>
+    <t>alberto694@gmail.com</t>
   </si>
   <si>
     <t>Celular</t>
   </si>
   <si>
-    <t>11119082536</t>
+    <t>11119082540</t>
   </si>
   <si>
     <t>Juan</t>
@@ -181,7 +184,7 @@
     <t>Pedro</t>
   </si>
   <si>
-    <t>50408042524</t>
+    <t>50408042529</t>
   </si>
   <si>
     <t>Hermano</t>
@@ -193,7 +196,7 @@
     <t>Laboral</t>
   </si>
   <si>
-    <t>50408042525</t>
+    <t>50408042527</t>
   </si>
   <si>
     <t>Nieto</t>
@@ -220,7 +223,7 @@
     <t>Armando</t>
   </si>
   <si>
-    <t>11119082517</t>
+    <t>11119082523</t>
   </si>
   <si>
     <t>Perez</t>
@@ -229,7 +232,7 @@
     <t>Julian</t>
   </si>
   <si>
-    <t>11119082518</t>
+    <t>11119082520</t>
   </si>
 </sst>
 </file>
@@ -699,7 +702,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -19687,85 +19690,85 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="B2" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="D3" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="8" t="s">
-        <v>41</v>
+      <c r="E3" s="7" t="s">
+        <v>45</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="F3" s="8" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>41</v>
-      </c>
       <c r="G3" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
       <c r="D4" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E4" s="9"/>
       <c r="F4" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G4" s="9"/>
     </row>
@@ -28766,75 +28769,75 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>53</v>
-      </c>
       <c r="D3" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="9"/>
       <c r="E4" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F4" s="9"/>
     </row>
@@ -36834,63 +36837,63 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
       <c r="D4" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E4" s="9"/>
     </row>

--- a/cypress/fixtures/ReferenciasPN.xlsx
+++ b/cypress/fixtures/ReferenciasPN.xlsx
@@ -76,7 +76,7 @@
     <t>Local</t>
   </si>
   <si>
-    <t>25145010000021</t>
+    <t>25145010000023</t>
   </si>
   <si>
     <t>Monetarios</t>
@@ -136,13 +136,13 @@
     <t>Correo Personal</t>
   </si>
   <si>
-    <t>alberto694@gmail.com</t>
+    <t>alberto696@gmail.com</t>
   </si>
   <si>
     <t>Celular</t>
   </si>
   <si>
-    <t>11119082540</t>
+    <t>11119082546</t>
   </si>
   <si>
     <t>Juan</t>

--- a/cypress/fixtures/ReferenciasPN.xlsx
+++ b/cypress/fixtures/ReferenciasPN.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="72">
   <si>
     <t>tieneReferenciasBancarias</t>
   </si>
@@ -67,7 +67,7 @@
     <t>institucionPrestamoReferenciaLaboralCliente</t>
   </si>
   <si>
-    <t>Si</t>
+    <t>No</t>
   </si>
   <si>
     <t>Cuentas</t>
@@ -104,9 +104,6 @@
   </si>
   <si>
     <t>Banco atlantida, s.a.</t>
-  </si>
-  <si>
-    <t>No</t>
   </si>
   <si>
     <t>tieneReferenciasComerciales</t>
@@ -717,7 +714,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -19705,25 +19702,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="2">
@@ -19731,59 +19728,59 @@
         <v>17</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="D2" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="E2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="G2" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="G2" s="3" t="s">
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>30</v>
+      <c r="C3" s="8" t="s">
+        <v>38</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="D3" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>39</v>
+      <c r="F3" s="9" t="s">
+        <v>41</v>
       </c>
-      <c r="D3" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E3" s="8" t="s">
+      <c r="G3" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="F3" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>46</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
       <c r="D4" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E4" s="10"/>
       <c r="F4" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G4" s="10"/>
     </row>
@@ -28784,75 +28781,75 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="1" t="s">
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" s="12" t="s">
+      <c r="C2" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="D2" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E2" s="9" t="s">
-        <v>42</v>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>17</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="B3" s="12" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>30</v>
+      <c r="C3" s="9" t="s">
+        <v>53</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="D3" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="8" t="s">
+      <c r="E3" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="F3" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="F3" s="8" t="s">
-        <v>60</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C4" s="9"/>
       <c r="D4" s="10"/>
       <c r="E4" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F4" s="10"/>
     </row>
@@ -36852,63 +36849,63 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D2" s="9" t="s">
-        <v>42</v>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>17</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="B3" s="8" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B3" s="8" t="s">
+      <c r="C3" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="D3" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="D3" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>72</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
       <c r="D4" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E4" s="10"/>
     </row>
